--- a/data_empty_test/reports/fraud_report.xlsx
+++ b/data_empty_test/reports/fraud_report.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="00_报告说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_核心指标_transactions_la" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="01_汇总" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ZZ_空数据集说明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="01_核心指标_主集" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Z7_覆盖率_主集" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="01_汇总" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ZZ_空数据集说明" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,39 +443,73 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46182.97871843549</v>
+        <v>46182.99325109065</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>输入文件数</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
+          <t>主分析集</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>transactions_labeled.pkl</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>分析维度</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>月份, 渠道, 商户类别(MCC), 省份, 城市, 交易类型, 收单行</t>
-        </is>
+          <t>输入文件数 (主+拆分)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>拆分补充集数</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>分析维度</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>月份, 渠道, 商户类别(MCC), 省份, 城市, 交易类型, 收单行</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>高风险特征Top</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B7" t="n">
         <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>口径说明</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>整体指标/月度趋势/维度/业务Markdown均基于主集；train/valid/backtest仅补充sheet</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -524,36 +559,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>总样本数</t>
+          <t>字段</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>_empty</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>文件</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="b">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>transactions_labeled.pkl</t>
+          <t>覆盖率</t>
         </is>
       </c>
     </row>
@@ -563,6 +580,60 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>总样本数</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>_empty</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>文件</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>transactions_labeled.pkl</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>主集(primary)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
